--- a/request_forms/050_logo_design_order_form--request_forms.xlsx
+++ b/request_forms/050_logo_design_order_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>washington</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>west_virginia</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -2219,29 +2219,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>wisconsin</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Wyoming</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>order_type_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>wyoming</t>
+          <t>one_time_order</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>One time order</t>
         </is>
       </c>
     </row>
@@ -2253,29 +2253,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>one_time_order</t>
+          <t>ongoing_order</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>One time order</t>
+          <t>Ongoing order</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>order_type_choices</t>
+          <t>order_frequency_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ongoing_order</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ongoing order</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -2321,29 +2321,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>order_frequency_choices</t>
+          <t>confirm_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>one-time</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>One-time</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2355,27 +2355,10 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>confirm_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
         <is>
           <t>False</t>
         </is>
